--- a/Project/outputs/tables/table_gru_metrics_h1.xlsx
+++ b/Project/outputs/tables/table_gru_metrics_h1.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0004620363761205226</v>
+        <v>0.0003812682989519089</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01097891945391893</v>
+        <v>0.009558992460370064</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02149503142869353</v>
+        <v>0.01952609277228573</v>
       </c>
       <c r="E2" t="n">
-        <v>6.872133255004883</v>
+        <v>6.097414493560791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5657894736842105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003379894187673926</v>
+        <v>0.0003945464268326759</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01015032548457384</v>
+        <v>0.01061086170375347</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01838448853700838</v>
+        <v>0.01986319276533045</v>
       </c>
       <c r="E3" t="n">
-        <v>6.763300895690918</v>
+        <v>5.861299991607666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5037593984962406</v>
+        <v>0.5601503759398496</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000308463757392019</v>
+        <v>0.0004208737518638372</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01021494902670383</v>
+        <v>0.01063986029475927</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01756313631991789</v>
+        <v>0.02051520781917252</v>
       </c>
       <c r="E4" t="n">
-        <v>6.104329109191895</v>
+        <v>6.015213489532471</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5281954887218046</v>
+        <v>0.5469924812030075</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0004622208944056183</v>
+        <v>0.0002662263868842274</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0131243048235774</v>
+        <v>0.0090531837195158</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02149932311505686</v>
+        <v>0.01631644528946876</v>
       </c>
       <c r="E5" t="n">
-        <v>8.151947975158691</v>
+        <v>5.320212841033936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5169172932330827</v>
+        <v>0.5883458646616542</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000434443267295137</v>
+        <v>0.0002386389096500352</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01225549541413784</v>
+        <v>0.009701288305222988</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02084330269643314</v>
+        <v>0.01544794192279461</v>
       </c>
       <c r="E6" t="n">
-        <v>5.652143478393555</v>
+        <v>5.231038570404053</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5639097744360902</v>
+        <v>0.5545112781954887</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002457638620398939</v>
+        <v>0.0002774399181362242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01014041155576706</v>
+        <v>0.01129840314388275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0156768575307647</v>
+        <v>0.0166565277935176</v>
       </c>
       <c r="E7" t="n">
-        <v>5.102965831756592</v>
+        <v>6.861868381500244</v>
       </c>
       <c r="F7" t="n">
-        <v>0.556390977443609</v>
+        <v>0.5394736842105263</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0005425327108241618</v>
+        <v>0.0002327863039681688</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01297941524535418</v>
+        <v>0.01003415137529373</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02329233158840398</v>
+        <v>0.01525733607049962</v>
       </c>
       <c r="E8" t="n">
-        <v>5.596199035644531</v>
+        <v>5.143669605255127</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5131578947368421</v>
+        <v>0.5394736842105263</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0002516343956813216</v>
+        <v>0.0001944403629750013</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008740457706153393</v>
+        <v>0.007568096276372671</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01586298823303231</v>
+        <v>0.01394418742612854</v>
       </c>
       <c r="E9" t="n">
-        <v>4.839202404022217</v>
+        <v>4.799743175506592</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5413533834586466</v>
+        <v>0.5225563909774437</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0003806355853157584</v>
+        <v>0.0003007775449077599</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01107303483877331</v>
+        <v>0.009808104659896344</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01932718243116385</v>
+        <v>0.01719086648239973</v>
       </c>
       <c r="E10" t="n">
-        <v>6.13527774810791</v>
+        <v>5.66630744934082</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5324248120300752</v>
+        <v>0.5521616541353385</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0001835842267610133</v>
+        <v>0.0001722407760098577</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00798029825091362</v>
+        <v>0.007609442342072725</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01354932569396032</v>
+        <v>0.01312405333766431</v>
       </c>
       <c r="E11" t="n">
-        <v>5.33001184463501</v>
+        <v>4.909061431884766</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5518617021276596</v>
+        <v>0.5554072096128171</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0001142518158303574</v>
+        <v>0.0001824098435463384</v>
       </c>
       <c r="C12" t="n">
-        <v>0.006922188214957714</v>
+        <v>0.008519151248037815</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01068886410383991</v>
+        <v>0.01350591883384238</v>
       </c>
       <c r="E12" t="n">
-        <v>5.906588077545166</v>
+        <v>5.942166805267334</v>
       </c>
       <c r="F12" t="n">
-        <v>0.550531914893617</v>
+        <v>0.5233644859813084</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0001333215332124382</v>
+        <v>0.0001356081629637629</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008311898447573185</v>
+        <v>0.007703449111431837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01154649441226376</v>
+        <v>0.01164509179713766</v>
       </c>
       <c r="E13" t="n">
-        <v>8.390006065368652</v>
+        <v>5.437384605407715</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5252659574468085</v>
+        <v>0.5126835781041389</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0002128479827661067</v>
+        <v>0.0001223053113790229</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01048522256314754</v>
+        <v>0.007665205746889114</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01458931056514004</v>
+        <v>0.01105917317791086</v>
       </c>
       <c r="E14" t="n">
-        <v>7.938446044921875</v>
+        <v>7.351995468139648</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.5260347129506008</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0004998999065719545</v>
+        <v>0.0004210557963233441</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01183415204286575</v>
+        <v>0.01011947356164455</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02235844150588217</v>
+        <v>0.02051964415684015</v>
       </c>
       <c r="E15" t="n">
-        <v>5.336073398590088</v>
+        <v>4.995322704315186</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5292553191489362</v>
+        <v>0.514018691588785</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0005733589641749859</v>
+        <v>0.0003617134934756905</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01269033551216125</v>
+        <v>0.01253850851207972</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02394491520500722</v>
+        <v>0.01901876687579114</v>
       </c>
       <c r="E16" t="n">
-        <v>5.233877182006836</v>
+        <v>7.202003955841064</v>
       </c>
       <c r="F16" t="n">
-        <v>0.538563829787234</v>
+        <v>0.514018691588785</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0002099082048516721</v>
+        <v>0.0005330184940248728</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009542739950120449</v>
+        <v>0.01131307985633612</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01448820916647989</v>
+        <v>0.02308719329032598</v>
       </c>
       <c r="E17" t="n">
-        <v>5.787317276000977</v>
+        <v>4.854056835174561</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5718085106382979</v>
+        <v>0.5353805073431241</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0002293001743964851</v>
+        <v>0.0002414236660115421</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007655880879610777</v>
+        <v>0.007437079213559628</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01514266074362379</v>
+        <v>0.01553781406799367</v>
       </c>
       <c r="E18" t="n">
-        <v>5.420414447784424</v>
+        <v>5.880535125732422</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5252659574468085</v>
+        <v>0.5006675567423231</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0002695591010706266</v>
+        <v>0.0002712219429668039</v>
       </c>
       <c r="C19" t="n">
-        <v>0.009427839482668787</v>
+        <v>0.009113173699006438</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01578852767452464</v>
+        <v>0.01593720694218827</v>
       </c>
       <c r="E19" t="n">
-        <v>6.167841911315918</v>
+        <v>5.821566104888916</v>
       </c>
       <c r="F19" t="n">
-        <v>0.543218085106383</v>
+        <v>0.5226969292389854</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
